--- a/서버정보/20260821_리소스배포_운영.xlsx
+++ b/서버정보/20260821_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A860CA-69DB-4EAA-BA1F-0E1D190E6818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919BBEAC-8844-4CC9-ACFE-837199089EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5624,10 +5624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.158.157.73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E4s_v5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5661,6 +5657,10 @@
   </si>
   <si>
     <t>10.158.156.70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.156.73</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6196,7 +6196,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6557,13 +6557,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24791,7 +24785,7 @@
       <c r="M132" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N132" s="123" t="s">
+      <c r="N132" s="121" t="s">
         <v>1050</v>
       </c>
       <c r="O132" s="74" t="str">
@@ -24880,7 +24874,7 @@
       <c r="M133" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N133" s="123" t="s">
+      <c r="N133" s="121" t="s">
         <v>1050</v>
       </c>
       <c r="O133" s="74" t="str">
@@ -24969,7 +24963,7 @@
       <c r="M134" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N134" s="123" t="s">
+      <c r="N134" s="121" t="s">
         <v>1050</v>
       </c>
       <c r="O134" s="74" t="str">
@@ -25058,7 +25052,7 @@
       <c r="M135" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N135" s="123" t="s">
+      <c r="N135" s="121" t="s">
         <v>1050</v>
       </c>
       <c r="O135" s="74" t="str">
@@ -25150,7 +25144,7 @@
         <v>1066</v>
       </c>
       <c r="O136" s="74" t="str">
-        <f>SUBSTITUTE(F136,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="O136:O141" si="14">SUBSTITUTE(F136,"hazr-","")&amp;"-osdisk"</f>
         <v>az-p-int-host1-osdisk</v>
       </c>
       <c r="P136" s="114">
@@ -25163,7 +25157,7 @@
       <c r="S136" s="95"/>
       <c r="T136" s="95"/>
       <c r="U136" s="95" t="str">
-        <f>SUBSTITUTE(F136,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U136:U141" si="15">SUBSTITUTE(F136,"hazr-","")&amp;"-nic"</f>
         <v>az-p-int-host1-nic</v>
       </c>
       <c r="V136" s="95" t="b">
@@ -25238,7 +25232,7 @@
         <v>1066</v>
       </c>
       <c r="O137" s="74" t="str">
-        <f>SUBSTITUTE(F137,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="14"/>
         <v>az-p-int-host2-osdisk</v>
       </c>
       <c r="P137" s="114">
@@ -25251,7 +25245,7 @@
       <c r="S137" s="95"/>
       <c r="T137" s="95"/>
       <c r="U137" s="95" t="str">
-        <f>SUBSTITUTE(F137,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="15"/>
         <v>az-p-int-host2-nic</v>
       </c>
       <c r="V137" s="95" t="b">
@@ -25326,7 +25320,7 @@
         <v>1066</v>
       </c>
       <c r="O138" s="74" t="str">
-        <f>SUBSTITUTE(F138,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="14"/>
         <v>az-p-int-host3-osdisk</v>
       </c>
       <c r="P138" s="114">
@@ -25339,7 +25333,7 @@
       <c r="S138" s="95"/>
       <c r="T138" s="95"/>
       <c r="U138" s="95" t="str">
-        <f>SUBSTITUTE(F138,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="15"/>
         <v>az-p-int-host3-nic</v>
       </c>
       <c r="V138" s="95" t="b">
@@ -25414,7 +25408,7 @@
         <v>1066</v>
       </c>
       <c r="O139" s="74" t="str">
-        <f>SUBSTITUTE(F139,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="14"/>
         <v>az-p-int-host4-osdisk</v>
       </c>
       <c r="P139" s="114">
@@ -25427,7 +25421,7 @@
       <c r="S139" s="95"/>
       <c r="T139" s="95"/>
       <c r="U139" s="95" t="str">
-        <f>SUBSTITUTE(F139,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="15"/>
         <v>az-p-int-host4-nic</v>
       </c>
       <c r="V139" s="95" t="b">
@@ -25461,14 +25455,15 @@
       <c r="AF139" s="95"/>
     </row>
     <row r="140" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A140" s="90"/>
       <c r="B140" s="95" t="s">
         <v>1067</v>
       </c>
-      <c r="C140" s="122" t="str" cm="1">
+      <c r="C140" s="95" t="str" cm="1">
         <f t="array" ref="C140">UPPER(INDEX(_xlfn.TEXTSPLIT($F140, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D140" s="122" t="s">
+      <c r="D140" s="95" t="s">
         <v>1068</v>
       </c>
       <c r="E140" s="95" t="s">
@@ -25481,7 +25476,7 @@
         <v>1075</v>
       </c>
       <c r="H140" s="95" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I140" s="95">
         <v>4</v>
@@ -25496,13 +25491,13 @@
         <v>178</v>
       </c>
       <c r="M140" s="95" t="s">
+        <v>1081</v>
+      </c>
+      <c r="N140" s="121" t="s">
         <v>1082</v>
       </c>
-      <c r="N140" s="123" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O140" s="120" t="str">
-        <f>SUBSTITUTE(F140,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O140" s="74" t="str">
+        <f t="shared" si="14"/>
         <v>p-bdp-rlgcweb01-osdisk</v>
       </c>
       <c r="P140" s="114">
@@ -25511,11 +25506,11 @@
       <c r="Q140" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R140" s="122"/>
+      <c r="R140" s="95"/>
       <c r="S140" s="95"/>
-      <c r="T140" s="122"/>
-      <c r="U140" s="122" t="str">
-        <f>SUBSTITUTE(F140,"hazr-","")&amp;"-nic"</f>
+      <c r="T140" s="95"/>
+      <c r="U140" s="95" t="str">
+        <f t="shared" si="15"/>
         <v>p-bdp-rlgcweb01-nic</v>
       </c>
       <c r="V140" s="95" t="b">
@@ -25549,14 +25544,15 @@
       <c r="AF140" s="95"/>
     </row>
     <row r="141" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A141" s="90"/>
       <c r="B141" s="95" t="s">
         <v>1067</v>
       </c>
-      <c r="C141" s="122" t="str" cm="1">
+      <c r="C141" s="95" t="str" cm="1">
         <f t="array" ref="C141">UPPER(INDEX(_xlfn.TEXTSPLIT($F141, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D141" s="122" t="s">
+      <c r="D141" s="95" t="s">
         <v>1068</v>
       </c>
       <c r="E141" s="95" t="s">
@@ -25569,7 +25565,7 @@
         <v>1076</v>
       </c>
       <c r="H141" s="95" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I141" s="95">
         <v>4</v>
@@ -25584,13 +25580,13 @@
         <v>178</v>
       </c>
       <c r="M141" s="95" t="s">
+        <v>1081</v>
+      </c>
+      <c r="N141" s="121" t="s">
         <v>1082</v>
       </c>
-      <c r="N141" s="123" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O141" s="120" t="str">
-        <f>SUBSTITUTE(F141,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O141" s="74" t="str">
+        <f t="shared" si="14"/>
         <v>p-bdp-rlgcweb02-osdisk</v>
       </c>
       <c r="P141" s="114">
@@ -25599,11 +25595,11 @@
       <c r="Q141" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R141" s="122"/>
+      <c r="R141" s="95"/>
       <c r="S141" s="95"/>
-      <c r="T141" s="122"/>
-      <c r="U141" s="122" t="str">
-        <f>SUBSTITUTE(F141,"hazr-","")&amp;"-nic"</f>
+      <c r="T141" s="95"/>
+      <c r="U141" s="95" t="str">
+        <f t="shared" si="15"/>
         <v>p-bdp-rlgcweb02-nic</v>
       </c>
       <c r="V141" s="95" t="b">
@@ -25637,14 +25633,15 @@
       <c r="AF141" s="95"/>
     </row>
     <row r="142" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A142" s="90"/>
       <c r="B142" s="74" t="s">
         <v>1067</v>
       </c>
-      <c r="C142" s="120" t="str" cm="1">
+      <c r="C142" s="74" t="str" cm="1">
         <f t="array" ref="C142">UPPER(INDEX(_xlfn.TEXTSPLIT($F142, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D142" s="122" t="s">
+      <c r="D142" s="95" t="s">
         <v>1068</v>
       </c>
       <c r="E142" s="74" t="s">
@@ -25657,7 +25654,7 @@
         <v>1077</v>
       </c>
       <c r="H142" s="74" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="I142" s="74">
         <v>16</v>
@@ -25672,13 +25669,13 @@
         <v>178</v>
       </c>
       <c r="M142" s="74" t="s">
+        <v>1081</v>
+      </c>
+      <c r="N142" s="122" t="s">
         <v>1082</v>
       </c>
-      <c r="N142" s="124" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O142" s="120" t="str">
-        <f t="shared" ref="O142:O144" si="14">SUBSTITUTE(F142,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O142" s="74" t="str">
+        <f t="shared" ref="O142:O144" si="16">SUBSTITUTE(F142,"hazr-","")&amp;"-osdisk"</f>
         <v>p-bdp-rlgcap01-osdisk</v>
       </c>
       <c r="P142" s="80">
@@ -25687,11 +25684,11 @@
       <c r="Q142" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="R142" s="120"/>
+      <c r="R142" s="74"/>
       <c r="S142" s="74"/>
-      <c r="T142" s="120"/>
-      <c r="U142" s="120" t="str">
-        <f t="shared" ref="U142:U144" si="15">SUBSTITUTE(F142,"hazr-","")&amp;"-nic"</f>
+      <c r="T142" s="74"/>
+      <c r="U142" s="74" t="str">
+        <f t="shared" ref="U142:U144" si="17">SUBSTITUTE(F142,"hazr-","")&amp;"-nic"</f>
         <v>p-bdp-rlgcap01-nic</v>
       </c>
       <c r="V142" s="74" t="b">
@@ -25725,14 +25722,15 @@
       <c r="AF142" s="74"/>
     </row>
     <row r="143" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A143" s="90"/>
       <c r="B143" s="74" t="s">
         <v>1069</v>
       </c>
-      <c r="C143" s="120" t="str" cm="1">
+      <c r="C143" s="74" t="str" cm="1">
         <f t="array" ref="C143">UPPER(INDEX(_xlfn.TEXTSPLIT($F143, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D143" s="122" t="s">
+      <c r="D143" s="95" t="s">
         <v>1068</v>
       </c>
       <c r="E143" s="74" t="s">
@@ -25745,7 +25743,7 @@
         <v>1078</v>
       </c>
       <c r="H143" s="74" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="I143" s="74">
         <v>16</v>
@@ -25760,13 +25758,13 @@
         <v>178</v>
       </c>
       <c r="M143" s="74" t="s">
+        <v>1081</v>
+      </c>
+      <c r="N143" s="119" t="s">
         <v>1082</v>
       </c>
-      <c r="N143" s="119" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O143" s="121" t="str">
-        <f t="shared" si="14"/>
+      <c r="O143" s="120" t="str">
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap02-osdisk</v>
       </c>
       <c r="P143" s="80">
@@ -25775,11 +25773,11 @@
       <c r="Q143" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="R143" s="120"/>
+      <c r="R143" s="74"/>
       <c r="S143" s="74"/>
-      <c r="T143" s="120"/>
-      <c r="U143" s="120" t="str">
-        <f t="shared" si="15"/>
+      <c r="T143" s="74"/>
+      <c r="U143" s="74" t="str">
+        <f t="shared" si="17"/>
         <v>p-bdp-rlgcap02-nic</v>
       </c>
       <c r="V143" s="74" t="b">
@@ -25813,14 +25811,15 @@
       <c r="AF143" s="74"/>
     </row>
     <row r="144" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A144" s="90"/>
       <c r="B144" s="74" t="s">
         <v>1067</v>
       </c>
-      <c r="C144" s="120" t="str" cm="1">
+      <c r="C144" s="74" t="str" cm="1">
         <f t="array" ref="C144">UPPER(INDEX(_xlfn.TEXTSPLIT($F144, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D144" s="122" t="s">
+      <c r="D144" s="95" t="s">
         <v>1068</v>
       </c>
       <c r="E144" s="74" t="s">
@@ -25830,10 +25829,10 @@
         <v>1074</v>
       </c>
       <c r="G144" s="74" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="H144" s="74" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="I144" s="74">
         <v>16</v>
@@ -25848,13 +25847,13 @@
         <v>178</v>
       </c>
       <c r="M144" s="74" t="s">
+        <v>1081</v>
+      </c>
+      <c r="N144" s="119" t="s">
         <v>1082</v>
       </c>
-      <c r="N144" s="119" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O144" s="121" t="str">
-        <f t="shared" si="14"/>
+      <c r="O144" s="120" t="str">
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap03-osdisk</v>
       </c>
       <c r="P144" s="80">
@@ -25863,11 +25862,11 @@
       <c r="Q144" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="R144" s="120"/>
+      <c r="R144" s="74"/>
       <c r="S144" s="74"/>
-      <c r="T144" s="120"/>
-      <c r="U144" s="120" t="str">
-        <f t="shared" si="15"/>
+      <c r="T144" s="74"/>
+      <c r="U144" s="74" t="str">
+        <f t="shared" si="17"/>
         <v>p-bdp-rlgcap03-nic</v>
       </c>
       <c r="V144" s="74" t="b">
@@ -33808,6 +33807,7 @@
       <c r="R148" s="80"/>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A149" s="99"/>
       <c r="B149" s="78" t="s">
         <v>23</v>
       </c>
@@ -33862,6 +33862,7 @@
       <c r="R149" s="78"/>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A150" s="99"/>
       <c r="B150" s="80" t="s">
         <v>23</v>
       </c>
@@ -33916,6 +33917,7 @@
       <c r="R150" s="80"/>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A151" s="99"/>
       <c r="B151" s="78" t="s">
         <v>23</v>
       </c>
@@ -33970,6 +33972,7 @@
       <c r="R151" s="78"/>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A152" s="99"/>
       <c r="B152" s="80" t="s">
         <v>23</v>
       </c>
@@ -34024,6 +34027,7 @@
       <c r="R152" s="80"/>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A153" s="99"/>
       <c r="B153" s="78" t="s">
         <v>23</v>
       </c>
@@ -40247,6 +40251,7 @@
       <c r="M157" s="118"/>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A158" s="90"/>
       <c r="B158" s="78" t="s">
         <v>23</v>
       </c>
@@ -40268,7 +40273,7 @@
         <v>345</v>
       </c>
       <c r="H158" s="117" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I158" s="117" t="s">
         <v>1070</v>
@@ -40286,6 +40291,7 @@
       <c r="M158" s="117"/>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A159" s="90"/>
       <c r="B159" s="80" t="s">
         <v>23</v>
       </c>
@@ -40307,7 +40313,7 @@
         <v>345</v>
       </c>
       <c r="H159" s="118" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I159" s="118" t="s">
         <v>1071</v>
@@ -40325,6 +40331,7 @@
       <c r="M159" s="118"/>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A160" s="90"/>
       <c r="B160" s="78" t="s">
         <v>23</v>
       </c>
@@ -40363,7 +40370,8 @@
       </c>
       <c r="M160" s="117"/>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A161" s="90"/>
       <c r="B161" s="80" t="s">
         <v>23</v>
       </c>
@@ -40402,7 +40410,8 @@
       </c>
       <c r="M161" s="118"/>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A162" s="90"/>
       <c r="B162" s="78" t="s">
         <v>23</v>
       </c>
@@ -45176,6 +45185,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="90"/>
       <c r="B43" s="74" t="s">
         <v>23</v>
       </c>
@@ -45190,7 +45200,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G43" s="74" t="s">
         <v>111</v>
@@ -45221,7 +45231,7 @@
         <v>108</v>
       </c>
       <c r="P43" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="Q43" s="74" t="str">
         <f t="shared" ref="Q43:Q44" si="6">SUBSTITUTE(F43, "hazr-", "")&amp;"-bp"</f>
@@ -45229,6 +45239,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="90"/>
       <c r="B44" s="82" t="s">
         <v>23</v>
       </c>
@@ -45243,7 +45254,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="82" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G44" s="82" t="s">
         <v>111</v>
@@ -45274,7 +45285,7 @@
         <v>108</v>
       </c>
       <c r="P44" s="82" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="Q44" s="82" t="str">
         <f t="shared" si="6"/>
@@ -47468,21 +47479,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -47626,10 +47622,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -47651,19 +47672,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>